--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-06 16:00:00</t>
+          <t>2026-08-06 11:00:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-06 20:30:00</t>
+          <t>2026-08-06 12:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-06 21:00:00</t>
+          <t>2026-08-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-06 21:00:00</t>
+          <t>2026-08-06 20:30:00</t>
         </is>
       </c>
     </row>
@@ -1255,141 +1255,467 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Termez Surkhon</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-1</v>
+      </c>
+      <c r="AN6">
+        <v>-1</v>
+      </c>
+      <c r="AO6">
+        <v>-1</v>
+      </c>
+      <c r="AP6">
+        <v>-1</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lokomotiv</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Xorazm</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Mash'al</t>
         </is>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
-      <c r="AN6">
-        <v>-1</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>-1</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>2026-08-06 21:00:00</t>
         </is>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,495 +1229,6 @@
       <c r="AU5" t="inlineStr">
         <is>
           <t>2026-08-06 20:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Termez Surkhon</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Navbahor</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
-      <c r="AN6">
-        <v>-1</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>-1</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2026-08-06 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Lokomotiv</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dinamo Samarqand</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-1</v>
-      </c>
-      <c r="AN7">
-        <v>-1</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>-1</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2026-08-06 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Xorazm</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mash'al</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-1</v>
-      </c>
-      <c r="AN8">
-        <v>-1</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>-1</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2026-08-06 21:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -970,16 +970,16 @@
         <v>2.77</v>
       </c>
       <c r="Q4">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
         <v>2.41</v>
@@ -991,13 +991,13 @@
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
         <v>1.64</v>
@@ -1006,7 +1006,7 @@
         <v>2.12</v>
       </c>
       <c r="AC4">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD4">
         <v>1.45</v>
@@ -1015,10 +1015,10 @@
         <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
         <v>2.3</v>
@@ -982,10 +982,10 @@
         <v>3.4</v>
       </c>
       <c r="U4">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -994,25 +994,25 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA4">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB4">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC4">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AD4">
         <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
         <v>1.52</v>
@@ -1130,7 +1130,7 @@
         <v>3.6</v>
       </c>
       <c r="P5">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q5">
         <v>3.1</v>
@@ -1145,13 +1145,13 @@
         <v>3.75</v>
       </c>
       <c r="U5">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
         <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1163,10 +1163,10 @@
         <v>5.4</v>
       </c>
       <c r="AA5">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB5">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC5">
         <v>2.2</v>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
         <v>3.5</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1015,7 +1015,7 @@
         <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
         <v>2.34</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R5">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA5">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AB5">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG5">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="S2">
         <v>1.33</v>
       </c>
       <c r="T2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
         <v>2.75</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>1.23</v>
@@ -680,19 +680,19 @@
         <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="AD2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -804,58 +804,58 @@
         <v>3.75</v>
       </c>
       <c r="P3">
-        <v>5.46</v>
+        <v>6.13</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="U3">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
         <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-08-06.xlsx
+++ b/jogos_2026-08-06.xlsx
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -624,42 +624,42 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R2">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -668,35 +668,35 @@
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA2">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
         <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -708,34 +708,34 @@
         <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -790,42 +790,42 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O3">
         <v>3.75</v>
       </c>
       <c r="P3">
-        <v>6.13</v>
+        <v>5.5</v>
       </c>
       <c r="Q3">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -834,71 +834,71 @@
         <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA3">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "28"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76", "83"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK3">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U4">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA4">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB4">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AC4">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG4">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
         <v>1.57</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
+        <v>2.4</v>
+      </c>
+      <c r="O5">
+        <v>3.15</v>
+      </c>
+      <c r="P5">
+        <v>2.6</v>
+      </c>
+      <c r="Q5">
         <v>3</v>
       </c>
-      <c r="O5">
-        <v>3.4</v>
-      </c>
-      <c r="P5">
-        <v>1.94</v>
-      </c>
-      <c r="Q5">
-        <v>3.5</v>
-      </c>
       <c r="R5">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
         <v>1.25</v>
@@ -1145,13 +1145,13 @@
         <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
         <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
+        <v>1.25</v>
+      </c>
+      <c r="AK5">
         <v>1.3</v>
-      </c>
-      <c r="AK5">
-        <v>1.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
